--- a/06.Look up Functions and Data Validation/Mileage+Trip.xlsx
+++ b/06.Look up Functions and Data Validation/Mileage+Trip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11020"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11023"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/spandanshelar/Documents/01-excle/06.Look up Functions and Data Validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{220F19DA-B8D5-C44A-88D7-FF2C8E2AD135}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FB7334-C12F-9948-B9EE-4CF9872EB52B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25600" windowHeight="16000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="14300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mileage" sheetId="1" r:id="rId1"/>
@@ -611,7 +611,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3">
         <v>0</v>
@@ -663,7 +663,7 @@
       </c>
       <c r="C5" s="6">
         <f>INDEX($H$4:$Q$13,MATCH(B4,$G$4:$G$13,0),MATCH(B5,$H$3:$Q$3,0))</f>
-        <v>68</v>
+        <v>197</v>
       </c>
       <c r="F5" s="1">
         <v>2</v>
@@ -938,7 +938,7 @@
       </c>
       <c r="C11" s="6">
         <f>SUM(C4:C9)</f>
-        <v>516</v>
+        <v>645</v>
       </c>
       <c r="F11" s="1">
         <v>8</v>
